--- a/gte/libraries/ВКНА-1В.xlsx
+++ b/gte/libraries/ВКНА-1В.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>T [С]</t>
   </si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>σ_500 [Па]</t>
+  </si>
+  <si>
+    <t>σ_1000 [Па]</t>
   </si>
 </sst>
 </file>
@@ -365,14 +368,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="4" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,8 +397,11 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>20</v>
       </c>
@@ -401,34 +410,37 @@
         <v>293.14999999999998</v>
       </c>
       <c r="C2" s="2">
-        <v>1350000000</v>
+        <v>725000000</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>900</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B6" si="0">A3+273.15</f>
+        <f t="shared" ref="B3:B8" si="0">A3+273.15</f>
         <v>1173.1500000000001</v>
       </c>
       <c r="C3" s="2">
-        <v>760000000</v>
+        <v>630000000</v>
       </c>
       <c r="D3" s="2">
-        <v>470000000</v>
+        <v>375000000</v>
       </c>
       <c r="E3" s="2">
-        <v>360000000</v>
+        <v>230000000</v>
       </c>
       <c r="F3" s="2">
-        <v>290000000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>170000000</v>
+      </c>
+      <c r="G3" s="2">
+        <v>145000000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1000</v>
       </c>
@@ -437,19 +449,22 @@
         <v>1273.1500000000001</v>
       </c>
       <c r="C4" s="2">
-        <v>520000000</v>
+        <v>475000000</v>
       </c>
       <c r="D4" s="2">
-        <v>290000000</v>
+        <v>255000000</v>
       </c>
       <c r="E4" s="2">
-        <v>200000000</v>
+        <v>125000000</v>
       </c>
       <c r="F4" s="2">
-        <v>150000000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>80000000</v>
+      </c>
+      <c r="G4" s="2">
+        <v>65000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1100</v>
       </c>
@@ -458,19 +473,22 @@
         <v>1373.15</v>
       </c>
       <c r="C5" s="2">
-        <v>410000000</v>
+        <v>395000000</v>
       </c>
       <c r="D5" s="2">
-        <v>140000000</v>
+        <v>105000000</v>
       </c>
       <c r="E5" s="2">
-        <v>100000000</v>
+        <v>60000000</v>
       </c>
       <c r="F5" s="2">
-        <v>75000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>40000000</v>
+      </c>
+      <c r="G5" s="2">
+        <v>35000000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1200</v>
       </c>
@@ -479,16 +497,49 @@
         <v>1473.15</v>
       </c>
       <c r="C6" s="2">
-        <v>210000000</v>
+        <v>225000000</v>
       </c>
       <c r="D6" s="2">
-        <v>90000000</v>
+        <v>65000000</v>
       </c>
       <c r="E6" s="2">
-        <v>50000000</v>
+        <v>39000000</v>
       </c>
       <c r="F6" s="2">
-        <v>30000000</v>
+        <v>27500000</v>
+      </c>
+      <c r="G6" s="2">
+        <v>23000000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1250</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>1523.15</v>
+      </c>
+      <c r="C7" s="2">
+        <v>135000000</v>
+      </c>
+      <c r="D7">
+        <v>22000000</v>
+      </c>
+      <c r="E7">
+        <v>13000000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1300</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>1573.15</v>
+      </c>
+      <c r="C8" s="2">
+        <v>65000000</v>
       </c>
     </row>
   </sheetData>
